--- a/多城市天气对比.xlsx
+++ b/多城市天气对比.xlsx
@@ -456,145 +456,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.94</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>9.369999999999999</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>clear sky</t>
+          <t>小雨</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-18 19:04:33</t>
+          <t>2026-03-28 22:05:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.92</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>5.55</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>moderate rain</t>
+          <t>阴</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-18 19:04:34</t>
+          <t>2026-03-28 22:05:17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.42</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>25.27</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>overcast clouds</t>
+          <t>小雨</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-18 19:04:35</t>
+          <t>2026-03-28 22:05:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chengdu</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.94</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>12.72</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>clear sky</t>
+          <t>小雨</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-18 19:04:37</t>
+          <t>2026-03-28 22:05:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Xi'an</t>
+          <t>西安区</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.45</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>10.48</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>overcast clouds</t>
+          <t>晴</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-18 19:04:38</t>
+          <t>2026-03-28 22:05:19</t>
         </is>
       </c>
     </row>
